--- a/output/pdf_financials_xlsx/EKG.xlsx
+++ b/output/pdf_financials_xlsx/EKG.xlsx
@@ -6375,13 +6375,13 @@
         <v>4.117331</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>4.305209</v>
+        <v>0.250403</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.169167</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.184894</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -6389,22 +6389,22 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.14969</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.14969</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.14969</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.14969</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.14969</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.218762</v>
       </c>
     </row>
     <row r="93">
@@ -6789,7 +6789,7 @@
         <v>-0.063606</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.000283</v>
+        <v>-0.000283</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>-0.002455</v>
@@ -11528,7 +11528,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -19706,7 +19710,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -21496,7 +21504,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -35629,7 +35641,7 @@
         <v>-0.063606</v>
       </c>
       <c r="R252" s="5" t="n">
-        <v>0.000283</v>
+        <v>-0.000283</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EKG.xlsx
+++ b/output/pdf_financials_xlsx/EKG.xlsx
@@ -1104,16 +1104,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000651</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002121</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002293</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>-0.302845</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.669656</v>
+        <v>-0.670307</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>-1.702764</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.9548990000000001</v>
+        <v>-0.957192</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.5997479999999999</v>
@@ -2319,7 +2319,7 @@
         <v>-0.282583</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.65426</v>
+        <v>-0.654911</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>-1.702764</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.9548990000000001</v>
+        <v>-0.957192</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.586187</v>
@@ -2386,7 +2386,7 @@
         <v>-15.29927694927275</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-28.73170508919977</v>
+        <v>-28.7602936320009</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>-100.4483934583282</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-63.44869148979996</v>
+        <v>-63.60105090119961</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-33.97452839155846</v>
@@ -8565,22 +8565,22 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022608</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02541</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02065</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02125</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0276</v>
       </c>
     </row>
     <row r="125">
@@ -8636,22 +8636,22 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022608</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02541</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02065</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02125</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0276</v>
       </c>
     </row>
     <row r="126">
@@ -30570,7 +30570,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -32978,7 +32982,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -34950,7 +34958,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -36636,7 +36648,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -47996,7 +48012,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -51606,7 +51622,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -53062,7 +53078,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -71212,7 +71228,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -73994,7 +74010,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -76658,7 +76674,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -78680,7 +78696,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">

--- a/output/pdf_financials_xlsx/EKG.xlsx
+++ b/output/pdf_financials_xlsx/EKG.xlsx
@@ -2266,37 +2266,37 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.013561</v>
+        <v>0.029056</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.004474</v>
+        <v>0.015495</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.001006</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.009539000000000001</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.010242</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.004411</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.022639</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.028725</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.02444</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.028987</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.02867</v>
       </c>
     </row>
     <row r="29">
@@ -2333,37 +2333,37 @@
         <v>-0.957192</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.586187</v>
+        <v>-0.570692</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.018583</v>
+        <v>-0.007562</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.039609</v>
+        <v>0.040615</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.577063</v>
+        <v>-0.567524</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.062108</v>
+        <v>-1.051866</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.063606</v>
+        <v>-0.059195</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.000283</v>
+        <v>0.022922</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.002455</v>
+        <v>0.02627</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.097326</v>
+        <v>-0.07288600000000001</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.194576</v>
+        <v>-0.165589</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.529488</v>
+        <v>-0.500818</v>
       </c>
     </row>
     <row r="30">
@@ -2400,37 +2400,37 @@
         <v>-63.60105090119961</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-33.97452839155846</v>
+        <v>-33.07646119213711</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-1.1930917145517</v>
+        <v>-0.4855060832718051</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2.276027441734583</v>
+        <v>2.333834596835317</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-53.65213041715788</v>
+        <v>-52.76524688442529</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-121.3993105403206</v>
+        <v>-120.2286464095976</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-7.619446923459333</v>
+        <v>-7.091047395437148</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.04146453317235912</v>
+        <v>3.358480669176028</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-0.2465319828803371</v>
+        <v>2.638042847359045</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-11.10502570702887</v>
+        <v>-8.316389286341842</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-36.94415542003053</v>
+        <v>-31.44039219558135</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-194.5516942364362</v>
+        <v>-184.0173722617009</v>
       </c>
     </row>
     <row r="31">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.020262</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.015396</v>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
@@ -6842,37 +6842,37 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.029056</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.004474</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.002104</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.009539000000000001</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.030101</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.024269</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.02863</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.028725</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.02444</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.028987</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.02867</v>
       </c>
     </row>
     <row r="101">
@@ -29498,7 +29498,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -29600,7 +29604,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -32352,7 +32360,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -32456,7 +32468,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -34242,7 +34258,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -34340,7 +34360,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -35902,7 +35926,11 @@
           <t>Depreciation of right of use assets</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -40578,7 +40606,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -43024,7 +43056,11 @@
           <t>Depreciation of property and equipment (note</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -43130,7 +43166,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -45042,7 +45078,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -47512,7 +47548,11 @@
           <t>Depreciation, property and equipment 7</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -47608,7 +47648,11 @@
           <t>Depreciation on right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -53184,7 +53228,11 @@
           <t>Depreciation on right of use assets 8</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -63508,7 +63556,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
